--- a/outputs/31628.xlsx
+++ b/outputs/31628.xlsx
@@ -104,16 +104,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -316,8 +320,8 @@
       <c r="A1" s="1" t="n">
         <v>45292</v>
       </c>
-      <c r="B1" s="0" t="n">
-        <v>10</v>
+      <c r="B1" s="2" t="n">
+        <v>45301</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -366,7 +370,7 @@
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2" t="n">
+      <c r="A11" s="3" t="n">
         <v>45301</v>
       </c>
     </row>

--- a/outputs/31628.xlsx
+++ b/outputs/31628.xlsx
@@ -21,9 +21,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -113,7 +114,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
